--- a/data/trans_dic/IP31KM11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,24; 100,0</t>
+          <t>91,0; 99,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,37; 99,12</t>
+          <t>92,14; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,02; 98,98</t>
+          <t>94,66; 99,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,3; 100,0</t>
+          <t>91,84; 98,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,06; 98,81</t>
+          <t>96,44; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,58; 99,07</t>
+          <t>95,56; 98,86</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,58; 99,72</t>
+          <t>97,64; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,78; 100,0</t>
+          <t>95,9; 99,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,9; 99,66</t>
+          <t>97,83; 99,65</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,76; 99,79</t>
+          <t>94,61; 98,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,6; 98,16</t>
+          <t>97,51; 99,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,59; 98,65</t>
+          <t>96,61; 98,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>98,12; 99,49</t>
+          <t>96,41; 98,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,87; 98,27</t>
+          <t>97,92; 99,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,37; 98,66</t>
+          <t>97,41; 98,74</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43727</t>
+          <t>41832</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89213</t>
+          <t>78098</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43350; 46495</t>
+          <t>34066; 37114</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40472; 44887</t>
+          <t>39327; 42681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86290; 90839</t>
+          <t>75838; 79347</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>256</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>157938</t>
+          <t>151201</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>176755</t>
+          <t>144195</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334694</t>
+          <t>295396</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155004; 159299</t>
+          <t>144222; 154550</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>171143; 179793</t>
+          <t>140338; 145518</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>329578; 338097</t>
+          <t>289137; 299101</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>230</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>170977</t>
+          <t>198777</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>210936</t>
+          <t>172294</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>381914</t>
+          <t>371072</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167152; 172580</t>
+          <t>195396; 200126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>207779; 212490</t>
+          <t>167509; 174022</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>377454; 384256</t>
+          <t>366683; 373480</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>337</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>271859</t>
+          <t>283842</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>291427</t>
+          <t>252756</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563286</t>
+          <t>536597</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>268123; 273692</t>
+          <t>276484; 288202</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>273270; 299378</t>
+          <t>248989; 254215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>542138; 571450</t>
+          <t>529010; 541861</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>904</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>646262</t>
+          <t>670086</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>640876; 649796</t>
+          <t>662166; 676812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>699061; 731853</t>
+          <t>605353; 614642</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1347114; 1379103</t>
+          <t>1271295; 1288578</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>91,0; 99,14</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>92,14; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>94,66; 99,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>91,84; 98,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>96,44; 100,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>95,56; 98,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>97,64; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>95,9; 99,63</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>97,83; 99,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>94,61; 98,62</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97,51; 99,56</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>96,61; 98,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>96,41; 98,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>97,92; 99,42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,41; 98,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9687613049092699</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9801103285797427</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9748073567823294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>36266</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41832</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>78098</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9100040167491266</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.92141921977802</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9465987383074659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>34066; 37114</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>39327; 42681</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>75838; 79347</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9914236937404763</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9903988277917891</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9628079887935289</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9909072471887179</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9763224732668693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>151201</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>144195</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>295396</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9183656659518624</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9644015395541664</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9556342869719519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>144222; 154550</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>140338; 145518</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>289137; 299101</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9841348025404937</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9885681390259825</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9932616205197083</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9863866660012856</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.990057591617909</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>198777</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>172294</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>371072</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.976365887638874</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.958994256171921</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9783478201117712</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>195396; 200126</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>167509; 174022</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>366683; 373480</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9962802489256131</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9964838544454646</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9713252453138287</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.989890403298393</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9799825468017404</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>283842</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>252756</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>536597</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9461469704942145</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9751368594967561</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9661252980034144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>276484; 288202</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>248989; 254215</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>529010; 541861</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.986246103680851</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9956048091798227</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9895964040963763</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9756298204601374</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9884645771174484</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9817097855636827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>670086</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>611077</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1281162</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9640991007794146</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9792056051391452</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9741489599954426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>662166; 676812</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>605353; 614642</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1271295; 1288578</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9854231660315677</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9942319274307645</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9873928727441982</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que utiliza aceite de oliva en casa (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>36266</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41832</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>78098</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>34066</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>39327</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>75838</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>37114</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42681</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>79347</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>151201</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>144195</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>295396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>144222</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>140338</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>289137</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>154550</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>145518</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>299101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>241</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>198777</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>172294</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>371072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>195396</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>167509</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>366683</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>200126</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>174022</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>373480</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>283842</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>252756</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>536597</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>276484</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>248989</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>529010</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>288202</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>254215</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>541861</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>904</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>670086</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>611077</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1281162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>662166</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>605353</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1271295</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>676812</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>614642</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1288578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>